--- a/data/trans_camb/IP09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 53,31</t>
+          <t>-14,92; 55,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 37,25</t>
+          <t>-26,24; 36,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 60,06</t>
+          <t>1,06; 60,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 22,73</t>
+          <t>-40,22; 23,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 68,15</t>
+          <t>-2,06; 68,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 20,76</t>
+          <t>-35,65; 22,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 28,19</t>
+          <t>-19,69; 29,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 47,62</t>
+          <t>-6,72; 49,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 30,25</t>
+          <t>-10,76; 30,02</t>
         </is>
       </c>
     </row>
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,81; —</t>
+          <t>-10,35; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 226,18</t>
+          <t>-100,0; 233,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 528,86</t>
+          <t>-4,95; 554,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,21; 193,21</t>
+          <t>-86,99; 206,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 241,54</t>
+          <t>-72,63; 262,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 388,65</t>
+          <t>-26,7; 437,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 282,65</t>
+          <t>-35,16; 263,08</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 53,02</t>
+          <t>6,8; 52,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,37 +903,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 59,2</t>
+          <t>8,78; 59,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 9,36</t>
+          <t>-56,22; 9,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 53,58</t>
+          <t>-19,25; 54,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 37,54</t>
+          <t>-41,47; 38,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 17,92</t>
+          <t>-23,74; 18,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,59; 70,57</t>
+          <t>15,26; 72,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 37,93</t>
+          <t>-10,78; 38,17</t>
         </is>
       </c>
     </row>
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,78; 534,75</t>
+          <t>-39,33; 488,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,32; 414,69</t>
+          <t>-83,17; 348,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-83,52; 335,0</t>
+          <t>-86,88; 291,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,26; 1155,13</t>
+          <t>35,94; 956,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,95; 588,52</t>
+          <t>-44,23; 661,46</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 57,79</t>
+          <t>7,69; 57,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1124,32 +1124,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-48,74; -4,32</t>
+          <t>-44,72; -3,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 45,8</t>
+          <t>-28,2; 44,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 32,5</t>
+          <t>-34,21; 37,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 9,43</t>
+          <t>-31,18; 8,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 50,86</t>
+          <t>-5,36; 54,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 35,11</t>
+          <t>-20,72; 36,23</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 67,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,41; 333,18</t>
+          <t>-75,43; 302,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 232,56</t>
+          <t>-100,0; 266,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-88,2; 129,38</t>
+          <t>-89,1; 123,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 466,35</t>
+          <t>-24,78; 583,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 338,49</t>
+          <t>-72,95; 290,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 26,39</t>
+          <t>-14,86; 26,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 23,08</t>
+          <t>-24,1; 22,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 54,11</t>
+          <t>-13,68; 54,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 42,08</t>
+          <t>0,16; 43,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 45,24</t>
+          <t>-12,13; 45,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 19,49</t>
+          <t>-19,29; 21,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 30,88</t>
+          <t>0,61; 30,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 25,22</t>
+          <t>-11,37; 25,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 30,27</t>
+          <t>-11,4; 31,97</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 192,89</t>
+          <t>-39,23; 183,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-63,74; 168,69</t>
+          <t>-66,78; 135,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,31; 481,93</t>
+          <t>-49,62; 505,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 346,1</t>
+          <t>-3,67; 375,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 337,67</t>
+          <t>-44,05; 368,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 166,16</t>
+          <t>-57,06; 166,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 189,89</t>
+          <t>1,78; 196,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 149,38</t>
+          <t>-37,81; 146,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,38; 191,84</t>
+          <t>-38,07; 204,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 45,48</t>
+          <t>-14,64; 44,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 58,5</t>
+          <t>-4,09; 57,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 31,78</t>
+          <t>-28,44; 35,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 21,59</t>
+          <t>-30,29; 19,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 24,08</t>
+          <t>-37,5; 21,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 24,4</t>
+          <t>-43,24; 27,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 23,68</t>
+          <t>-17,37; 22,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 33,98</t>
+          <t>-12,23; 34,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 20,71</t>
+          <t>-29,25; 19,83</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-44,18; 558,57</t>
+          <t>-38,41; 681,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 799,3</t>
+          <t>-12,83; 842,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,32; 502,59</t>
+          <t>-70,44; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 131,36</t>
+          <t>-64,36; 114,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-81,33; 159,6</t>
+          <t>-84,12; 109,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,94; 96,87</t>
+          <t>-84,37; 109,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,13; 130,84</t>
+          <t>-41,33; 118,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 192,51</t>
+          <t>-34,35; 181,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-67,89; 91,68</t>
+          <t>-72,77; 90,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-53,98; 57,73</t>
+          <t>-59,2; 47,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-69,93; 51,36</t>
+          <t>-65,19; 54,39</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 71,86</t>
+          <t>-37,78; 70,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 44,38</t>
+          <t>-38,13; 46,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 66,07</t>
+          <t>-16,29; 65,42</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 68,22</t>
+          <t>-9,38; 68,63</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 34,23</t>
+          <t>-28,53; 33,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 48,03</t>
+          <t>-21,19; 47,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 60,2</t>
+          <t>-5,68; 57,99</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-89,12; 394,16</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-59,25; 555,7</t>
+          <t>-56,19; 530,55</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,08; 232,19</t>
+          <t>-62,62; 241,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 404,43</t>
+          <t>-25,67; 403,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 366,93</t>
+          <t>-15,94; 424,56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-58,24; 141,18</t>
+          <t>-51,77; 150,13</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 189,52</t>
+          <t>-36,87; 203,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 249,44</t>
+          <t>-10,68; 233,53</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,56; 26,38</t>
+          <t>0,32; 25,23</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,48; 34,21</t>
+          <t>5,44; 36,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,01; 36,89</t>
+          <t>4,88; 39,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 12,9</t>
+          <t>-9,58; 13,22</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,72; 29,43</t>
+          <t>3,49; 32,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 11,07</t>
+          <t>-13,81; 11,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 15,56</t>
+          <t>-1,9; 15,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,46; 27,24</t>
+          <t>6,57; 28,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 18,33</t>
+          <t>-2,72; 18,51</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6,91; 196,52</t>
+          <t>-1,28; 181,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>15,74; 248,74</t>
+          <t>16,98; 258,51</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6,93; 255,3</t>
+          <t>13,85; 247,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 51,56</t>
+          <t>-27,5; 54,45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,44; 120,87</t>
+          <t>8,91; 132,44</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 43,89</t>
+          <t>-39,93; 47,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 71,44</t>
+          <t>-6,6; 76,54</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>22,81; 130,65</t>
+          <t>20,83; 127,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 82,36</t>
+          <t>-11,04; 88,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 55,11</t>
+          <t>-12,74; 56,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 36,14</t>
+          <t>-27,15; 32,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 60,23</t>
+          <t>1,25; 62,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 23,55</t>
+          <t>-40,24; 22,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 68,57</t>
+          <t>-5,32; 64,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 22,91</t>
+          <t>-34,66; 22,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 29,09</t>
+          <t>-18,12; 29,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 49,99</t>
+          <t>-4,68; 48,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 30,02</t>
+          <t>-9,21; 33,19</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,35; —</t>
+          <t>-21,25; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 233,43</t>
+          <t>-100,0; 243,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 554,93</t>
+          <t>-10,15; 555,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,99; 206,55</t>
+          <t>-85,16; 195,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 262,54</t>
+          <t>-66,46; 314,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 437,68</t>
+          <t>-18,13; 453,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 263,08</t>
+          <t>-30,03; 321,52</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 52,56</t>
+          <t>6,78; 52,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,37 +903,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 59,26</t>
+          <t>9,14; 59,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,22; 9,44</t>
+          <t>-55,61; 2,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 54,53</t>
+          <t>-18,78; 53,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 38,1</t>
+          <t>-37,0; 38,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 18,2</t>
+          <t>-22,54; 18,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,26; 72,13</t>
+          <t>16,97; 73,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 38,17</t>
+          <t>-11,05; 36,83</t>
         </is>
       </c>
     </row>
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 488,96</t>
+          <t>-36,09; 546,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,17; 348,0</t>
+          <t>-83,84; 339,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-86,88; 291,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,94; 956,04</t>
+          <t>45,46; 1368,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,23; 661,46</t>
+          <t>-54,16; 536,28</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 57,65</t>
+          <t>7,03; 57,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1124,32 +1124,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-44,72; -3,65</t>
+          <t>-48,98; -4,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 44,89</t>
+          <t>-27,64; 47,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 37,16</t>
+          <t>-33,47; 34,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 8,91</t>
+          <t>-31,75; 8,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 54,0</t>
+          <t>-8,44; 51,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 36,23</t>
+          <t>-19,69; 36,03</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 150,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,43; 302,15</t>
+          <t>-77,21; 358,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 266,46</t>
+          <t>-100,0; 276,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,1; 123,37</t>
+          <t>-88,02; 104,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 583,66</t>
+          <t>-34,45; 438,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 290,4</t>
+          <t>-71,56; 296,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 26,73</t>
+          <t>-15,52; 25,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 22,0</t>
+          <t>-23,39; 23,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 54,15</t>
+          <t>-18,15; 52,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 43,36</t>
+          <t>3,29; 42,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 45,83</t>
+          <t>-11,78; 44,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 21,4</t>
+          <t>-19,4; 19,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 30,49</t>
+          <t>0,04; 29,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 25,28</t>
+          <t>-13,05; 24,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 31,97</t>
+          <t>-11,89; 29,52</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 183,54</t>
+          <t>-37,43; 177,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 135,39</t>
+          <t>-64,44; 173,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 505,63</t>
+          <t>-58,91; 541,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 375,43</t>
+          <t>9,37; 402,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 368,54</t>
+          <t>-43,42; 348,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,06; 166,09</t>
+          <t>-58,46; 165,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 196,41</t>
+          <t>-0,18; 171,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 146,43</t>
+          <t>-42,46; 131,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 204,72</t>
+          <t>-40,73; 151,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 44,78</t>
+          <t>-16,18; 43,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 57,95</t>
+          <t>-1,49; 57,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 35,28</t>
+          <t>-27,51; 32,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 19,84</t>
+          <t>-27,66; 21,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 21,82</t>
+          <t>-35,17; 23,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 27,02</t>
+          <t>-38,72; 27,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 22,44</t>
+          <t>-16,26; 23,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 34,48</t>
+          <t>-10,81; 35,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 19,83</t>
+          <t>-26,69; 21,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 681,39</t>
+          <t>-41,32; 584,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 842,04</t>
+          <t>-13,33; 755,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,44; —</t>
+          <t>-78,67; 508,94</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-64,36; 114,9</t>
+          <t>-62,71; 113,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-84,12; 109,82</t>
+          <t>-84,49; 120,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,37; 109,91</t>
+          <t>-80,76; 117,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-41,33; 118,7</t>
+          <t>-42,02; 136,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 181,39</t>
+          <t>-29,85; 184,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-72,77; 90,51</t>
+          <t>-65,36; 93,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-59,2; 47,23</t>
+          <t>-49,03; 47,72</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 54,39</t>
+          <t>-71,19; 52,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 70,28</t>
+          <t>-38,2; 68,47</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 46,11</t>
+          <t>-35,41; 45,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 65,42</t>
+          <t>-10,6; 65,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 68,63</t>
+          <t>-16,9; 68,09</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 33,45</t>
+          <t>-31,46; 34,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 47,34</t>
+          <t>-18,09; 52,93</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 57,99</t>
+          <t>-9,11; 57,54</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-89,12; 394,16</t>
+          <t>-78,07; 349,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-56,19; 530,55</t>
+          <t>-59,58; 476,52</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-62,62; 241,29</t>
+          <t>-63,41; 230,13</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 403,4</t>
+          <t>-16,76; 396,54</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 424,56</t>
+          <t>-24,31; 350,97</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 150,13</t>
+          <t>-57,5; 137,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 203,75</t>
+          <t>-31,44; 223,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 233,53</t>
+          <t>-14,94; 261,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,32; 25,23</t>
+          <t>1,18; 26,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,44; 36,15</t>
+          <t>6,15; 35,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,88; 39,67</t>
+          <t>3,4; 36,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 13,22</t>
+          <t>-9,45; 13,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,49; 32,41</t>
+          <t>1,3; 29,71</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 11,92</t>
+          <t>-13,66; 11,55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 15,78</t>
+          <t>-1,07; 15,4</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,57; 28,15</t>
+          <t>7,61; 27,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 18,51</t>
+          <t>-3,14; 18,52</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 181,71</t>
+          <t>4,59; 210,68</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16,98; 258,51</t>
+          <t>19,6; 264,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13,85; 247,5</t>
+          <t>10,07; 270,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 54,45</t>
+          <t>-26,71; 56,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,91; 132,44</t>
+          <t>3,04; 121,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-39,93; 47,93</t>
+          <t>-40,53; 45,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 76,54</t>
+          <t>-4,69; 68,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,83; 127,22</t>
+          <t>25,28; 129,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 88,26</t>
+          <t>-11,22; 79,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-9,99</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35,87</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>18,62</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>33,55</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-9,99</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,87</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,74</t>
+          <t>33,34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,96</t>
+          <t>12,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 56,3</t>
+          <t>-40,17; 22,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 32,13</t>
+          <t>-2,83; 68,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 62,47</t>
+          <t>-34,36; 23,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 22,86</t>
+          <t>-13,88; 53,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 64,48</t>
+          <t>-25,87; 37,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 22,08</t>
+          <t>-1,66; 59,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 29,26</t>
+          <t>-19,12; 28,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 48,08</t>
+          <t>-1,4; 47,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 33,19</t>
+          <t>-8,66; 32,35</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-35,01%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-21,04%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>138,21%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-2,96%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>249,09%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-35,01%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>125,71%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-23,62%</t>
+          <t>247,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>55,65%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 226,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-11,13; 528,86</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-84,92; 201,47</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-21,25; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 243,39</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 555,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,16; 195,32</t>
+          <t>-29,82; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,46; 314,39</t>
+          <t>-71,14; 241,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 453,69</t>
+          <t>-12,15; 388,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 321,52</t>
+          <t>-29,7; 291,03</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-24,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20,51</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>22,06</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>100,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-24,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,51</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>26,76</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,15</t>
+          <t>13,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 52,2</t>
+          <t>-56,15; 9,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>-21,69; 53,58</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>-35,49; 40,07</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6,92; 53,02</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,14; 59,47</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-55,61; 2,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-18,78; 53,09</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 38,27</t>
+          <t>7,84; 57,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 18,55</t>
+          <t>-22,58; 17,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,97; 73,28</t>
+          <t>14,59; 70,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 36,83</t>
+          <t>-10,39; 38,95</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-72,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>62,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-72,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>62,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-2,04%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>-11,01%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>-43,78; 534,75</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-78,15; 417,67</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-36,09; 546,55</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-83,84; 339,01</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,52; 335,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,46; 1368,06</t>
+          <t>40,26; 1155,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 536,28</t>
+          <t>-49,57; 610,95</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-23,92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,03</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,74</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>24,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>65,06</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-23,92</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,03</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>38,39</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>8,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 57,5</t>
+          <t>-48,74; -4,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>-27,35; 45,8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>-30,77; 35,92</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7,42; 57,79</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>20,49; 100,0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-48,98; -4,46</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-27,64; 47,51</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-33,47; 34,64</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 8,15</t>
+          <t>-31,08; 9,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 51,28</t>
+          <t>-12,19; 50,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 36,03</t>
+          <t>-18,28; 37,08</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-82,87%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-2,56%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-82,87%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-7,48%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-43,67%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 67,93</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-74,41; 333,18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-84,99; 267,24</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 150,15</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-77,21; 358,95</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 276,79</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-88,02; 104,25</t>
+          <t>-88,2; 129,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 438,09</t>
+          <t>-39,26; 466,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,56; 296,11</t>
+          <t>-65,91; 350,4</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>24,53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16,14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,37</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,01</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,89</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24,53</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,14</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>-3,87</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>-0,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 25,99</t>
+          <t>1,54; 42,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 23,33</t>
+          <t>-12,67; 45,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 52,95</t>
+          <t>-19,89; 21,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 42,69</t>
+          <t>-18,06; 26,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 44,96</t>
+          <t>-24,52; 23,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 19,02</t>
+          <t>-27,93; 23,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 29,29</t>
+          <t>1,56; 30,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 24,05</t>
+          <t>-11,56; 25,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 29,52</t>
+          <t>-15,74; 15,75</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>104,9%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>69,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>22,19%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-7,13%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>38,66%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>104,9%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>69,0%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>-13,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>-1,76%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 177,63</t>
+          <t>-0,92; 346,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 173,36</t>
+          <t>-46,94; 337,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 541,32</t>
+          <t>-61,73; 182,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,37; 402,6</t>
+          <t>-41,32; 192,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 348,05</t>
+          <t>-63,74; 168,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 165,21</t>
+          <t>-72,33; 167,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 171,9</t>
+          <t>4,08; 189,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,46; 131,74</t>
+          <t>-36,54; 149,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 151,4</t>
+          <t>-46,89; 97,05</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-3,99</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-8,92</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,05</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>17,67</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>30,92</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4,27</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,99</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-8,92</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,67</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-1,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 43,32</t>
+          <t>-26,6; 21,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 57,42</t>
+          <t>-34,17; 24,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 32,71</t>
+          <t>-39,49; 23,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 21,84</t>
+          <t>-13,94; 45,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 23,29</t>
+          <t>-3,91; 58,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 27,9</t>
+          <t>-28,8; 32,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 23,42</t>
+          <t>-14,4; 23,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 35,58</t>
+          <t>-12,04; 33,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 21,1</t>
+          <t>-26,18; 20,62</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-12,01%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-26,86%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-15,21%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>78,34%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>137,05%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>18,93%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-12,01%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-26,86%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-17,06%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-7,34%</t>
+          <t>-5,91%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 584,23</t>
+          <t>-60,07; 131,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 755,81</t>
+          <t>-81,33; 159,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,67; 508,94</t>
+          <t>-83,05; 101,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 113,01</t>
+          <t>-44,18; 558,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-84,49; 120,61</t>
+          <t>-20,54; 799,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,76; 117,0</t>
+          <t>-73,18; 507,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 136,03</t>
+          <t>-39,13; 130,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 184,0</t>
+          <t>-29,72; 192,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,36; 93,4</t>
+          <t>-64,81; 96,01</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4,56</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>30,52</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>33,17</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-0,89</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-17,65</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>20,62</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>30,52</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,66</t>
+          <t>16,34</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28,85</t>
+          <t>25,9</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 47,72</t>
+          <t>-31,61; 44,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-71,19; 52,06</t>
+          <t>-15,3; 66,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 68,47</t>
+          <t>-18,15; 67,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 45,79</t>
+          <t>-53,98; 57,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 65,29</t>
+          <t>-69,93; 51,36</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 68,09</t>
+          <t>-44,8; 70,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 34,11</t>
+          <t>-31,3; 34,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 52,93</t>
+          <t>-18,49; 48,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 57,54</t>
+          <t>-11,98; 58,49</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>75,49%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>82,04%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-1,98%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-39,22%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>45,84%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>75,49%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-78,07; 349,26</t>
+          <t>-63,08; 232,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>-23,75; 404,43</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-28,22; 335,26</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-59,58; 476,52</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-63,41; 230,13</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 396,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 350,97</t>
+          <t>-69,23; 494,28</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-57,5; 137,8</t>
+          <t>-58,24; 141,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-31,44; 223,97</t>
+          <t>-34,48; 189,52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 261,78</t>
+          <t>-21,25; 241,92</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2,31</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>16,55</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,19</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>13,69</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>20,29</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>18,03</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>16,55</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>12,76</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>5,25</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 26,27</t>
+          <t>-9,94; 12,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,15; 35,28</t>
+          <t>0,72; 29,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,4; 36,87</t>
+          <t>-13,04; 12,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 13,7</t>
+          <t>2,56; 26,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,3; 29,71</t>
+          <t>4,48; 34,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 11,55</t>
+          <t>-0,61; 25,88</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 15,4</t>
+          <t>-1,21; 15,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>7,61; 27,62</t>
+          <t>6,46; 27,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 18,52</t>
+          <t>-4,38; 14,49</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>68,35%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>101,25%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-3,21%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>4,59; 210,68</t>
+          <t>-28,33; 51,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19,6; 264,81</t>
+          <t>1,44; 120,87</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10,07; 270,75</t>
+          <t>-35,62; 50,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 56,52</t>
+          <t>6,91; 196,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,04; 121,56</t>
+          <t>15,74; 248,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 45,1</t>
+          <t>-5,78; 188,29</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 68,57</t>
+          <t>-5,27; 71,44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>25,28; 129,11</t>
+          <t>22,81; 130,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 79,28</t>
+          <t>-14,51; 66,14</t>
         </is>
       </c>
     </row>
